--- a/SeleniumTests/TestDataFolder/LoginTestDataNegative.xlsx
+++ b/SeleniumTests/TestDataFolder/LoginTestDataNegative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F8B71D-9ACC-477B-8445-C1DAA44C9B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C67169-CACF-440B-9C59-70F63C0A0DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WrongUserAndPasswordTestData" sheetId="1" r:id="rId1"/>
@@ -46,18 +46,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
   <si>
-    <t>email</t>
-  </si>
-  <si>
     <t>yanshen.choo@qubeapps.com</t>
   </si>
   <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
     <t>invalidUser@qubeapps.com</t>
   </si>
   <si>
@@ -89,6 +80,15 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
 </sst>
 </file>
@@ -419,21 +419,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -445,21 +449,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBBB11A-0026-4DA9-A2A3-9A7402989093}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -474,19 +482,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B83557B-C865-4131-81D7-0B527DE63C8C}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -498,18 +510,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2ACBDB7-B53C-4BDD-9536-05C23AE768B9}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -521,21 +537,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90FCBD3-969E-4BF4-8164-C8F6DAFC2AB7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -550,12 +570,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -570,12 +590,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -587,15 +607,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C2F6E9-6ADE-4B49-9414-17338C880892}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -607,15 +630,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7231BB1-A134-495E-A520-665003E209CA}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
